--- a/outputs/Прогноз остатков.xlsx
+++ b/outputs/Прогноз остатков.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПРОГНОЗ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="КОНЧИТСЯ ДО ЯНВАРЯ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="КОНЧИТСЯ ДО МАЯ" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="92" customWidth="1" min="1" max="1"/>
@@ -468,11 +468,15 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,15 +517,35 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток на 01.01, шт</t>
+          <t>Январь</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Февраль х2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Март х1,5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток на 01.05, шт</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Хватит до</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Запас, месяцев</t>
         </is>
@@ -554,12 +578,24 @@
       <c r="H2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>сентябрь 2026</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -590,12 +626,24 @@
       <c r="H3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>сентябрь 2026</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -626,12 +674,24 @@
       <c r="H4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>октябрь 2026</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="N4" s="2" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -662,12 +722,24 @@
       <c r="H5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>октябрь 2026</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="N5" s="2" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -698,12 +770,24 @@
       <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>октябрь 2026</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="N6" s="2" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -734,12 +818,24 @@
       <c r="H7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="N7" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -770,12 +866,24 @@
       <c r="H8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -806,12 +914,24 @@
       <c r="H9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -842,12 +962,24 @@
       <c r="H10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="N10" s="2" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -878,12 +1010,24 @@
       <c r="H11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="N11" s="2" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -914,12 +1058,24 @@
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="N12" s="2" t="n">
         <v>2.7</v>
       </c>
     </row>
@@ -950,12 +1106,24 @@
       <c r="H13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="N13" s="2" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -986,12 +1154,24 @@
       <c r="H14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>декабрь 2026</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="N14" s="2" t="n">
         <v>3.5</v>
       </c>
     </row>
@@ -1022,12 +1202,24 @@
       <c r="H15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>декабрь 2026</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="N15" s="2" t="n">
         <v>3.5</v>
       </c>
     </row>
@@ -1058,12 +1250,24 @@
       <c r="H16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>декабрь 2026</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="N16" s="2" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -1094,12 +1298,24 @@
       <c r="H17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>декабрь 2026</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="N17" s="2" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -1130,12 +1346,24 @@
       <c r="H18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>декабрь 2026</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="N18" s="2" t="n">
         <v>3.9</v>
       </c>
     </row>
@@ -1166,12 +1394,24 @@
       <c r="H19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>декабрь 2026</t>
         </is>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="N19" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1202,12 +1442,24 @@
       <c r="H20" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>январь 2027</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="N20" s="4" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -1238,12 +1490,24 @@
       <c r="H21" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>январь 2027</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="N21" s="4" t="n">
         <v>4.8</v>
       </c>
     </row>
@@ -1272,15 +1536,27 @@
         <v>180</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>129</v>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
+        <v>90</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>февраль 2027</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n">
-        <v>5.4</v>
+      <c r="N22" s="4" t="n">
+        <v>5.2</v>
       </c>
     </row>
     <row r="23">
@@ -1308,15 +1584,27 @@
         <v>20</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>февраль 2027</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>5.7</v>
+      <c r="N23" s="4" t="n">
+        <v>5.3</v>
       </c>
     </row>
     <row r="24">
@@ -1344,15 +1632,27 @@
         <v>98</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>март 2027</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>6.5</v>
+        <v>49</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>февраль 2027</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>5.7</v>
       </c>
     </row>
     <row r="25">
@@ -1380,15 +1680,27 @@
         <v>68</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>113</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>апрель 2027</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>7.3</v>
+        <v>34</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>март 2027</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>6.2</v>
       </c>
     </row>
     <row r="26">
@@ -1416,231 +1728,315 @@
         <v>684</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>1231</v>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
+        <v>342</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>684</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>март 2027</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>901</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>март 2027</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>259</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>март 2027</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3239</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>488</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>476</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>март 2027</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>7340</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>709</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>709</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>709</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1064</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1418</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>709</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1418</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>1064</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>апрель 2027</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>901</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>94</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>94</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>94</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>141</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>188</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>384</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>май 2027</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>259</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>111</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>май 2027</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>3239</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>325</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>325</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>325</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>488</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>650</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>1451</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>май 2027</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>7340</v>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>709</v>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v>709</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>709</v>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>1064</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>1418</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>3440</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>май 2027</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>8.9</v>
+      <c r="N30" s="4" t="n">
+        <v>7.4</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="5" t="n">
         <v>759</v>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="C31" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="5" t="n">
         <v>142</v>
       </c>
-      <c r="H31" s="6" t="n">
-        <v>369</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>июнь 2027</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>9.199999999999999</v>
+      <c r="H31" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>апрель 2027</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>7.7</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="5" t="n">
         <v>6179</v>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C32" s="5" t="n">
         <v>563</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="5" t="n">
         <v>563</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="5" t="n">
         <v>563</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="5" t="n">
         <v>844</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="5" t="n">
         <v>1126</v>
       </c>
-      <c r="H32" s="6" t="n">
-        <v>3083</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>июнь 2027</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>9.5</v>
+      <c r="H32" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>1126</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>844</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>549</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>апрель 2027</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -1668,15 +2064,27 @@
         <v>10</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>июнь 2027</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>9.9</v>
+        <v>5</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>май 2027</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="34">
@@ -1704,15 +2112,27 @@
         <v>128</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>480</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>август 2027</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>11.5</v>
+        <v>64</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>июль 2027</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -1740,15 +2160,27 @@
         <v>2</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>август 2027</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>11.5</v>
+        <v>1</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>июль 2027</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -1776,15 +2208,27 @@
         <v>364</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1434</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>август 2027</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>11.9</v>
+        <v>182</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>273</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>182</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>433</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>июль 2027</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>10.4</v>
       </c>
     </row>
     <row r="37">
@@ -1812,15 +2256,27 @@
         <v>130</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>583</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>сентябрь 2027</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>13</v>
+        <v>65</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="L37" s="6" t="n">
+        <v>225</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>август 2027</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>11.5</v>
       </c>
     </row>
     <row r="38">
@@ -1848,15 +2304,27 @@
         <v>192</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>894</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>октябрь 2027</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>13.3</v>
+        <v>96</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>192</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="L38" s="6" t="n">
+        <v>366</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>август 2027</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>11.8</v>
       </c>
     </row>
     <row r="39">
@@ -1884,15 +2352,27 @@
         <v>32</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>152</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>октябрь 2027</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>13.5</v>
+        <v>16</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="L39" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>сентябрь 2027</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="40">
@@ -1920,15 +2400,27 @@
         <v>82</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>424</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>ноябрь 2027</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>14.2</v>
+        <v>41</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="L40" s="6" t="n">
+        <v>198</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>сентябрь 2027</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>12.9</v>
       </c>
     </row>
     <row r="41">
@@ -1956,15 +2448,27 @@
         <v>32</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>212</v>
-      </c>
-      <c r="I41" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="L41" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>декабрь 2027</t>
         </is>
       </c>
-      <c r="J41" t="n">
-        <v>15.9</v>
+      <c r="N41" t="n">
+        <v>15.1</v>
       </c>
     </row>
     <row r="42">
@@ -1992,15 +2496,27 @@
         <v>42</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>289</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>январь 2028</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>16.3</v>
+        <v>21</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="L42" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>декабрь 2027</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>15.4</v>
       </c>
     </row>
     <row r="43">
@@ -2028,15 +2544,27 @@
         <v>154</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>1076</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>январь 2028</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>16.5</v>
+        <v>77</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>154</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>116</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L43" s="6" t="n">
+        <v>652</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>декабрь 2027</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>15.5</v>
       </c>
     </row>
     <row r="44">
@@ -2064,15 +2592,27 @@
         <v>136</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>981</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>январь 2028</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>16.9</v>
+        <v>68</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>136</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="L44" s="6" t="n">
+        <v>607</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>декабрь 2027</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>15.7</v>
       </c>
     </row>
     <row r="45">
@@ -2100,15 +2640,27 @@
         <v>72</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>602</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>апрель 2028</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>19.2</v>
+        <v>36</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="L45" s="6" t="n">
+        <v>404</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>февраль 2028</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>17.4</v>
       </c>
     </row>
     <row r="46">
@@ -2136,15 +2688,27 @@
         <v>548</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>5956</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>сентябрь 2028</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>24.2</v>
+        <v>274</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>548</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>411</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>274</v>
+      </c>
+      <c r="L46" s="6" t="n">
+        <v>4449</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>июнь 2028</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>21.2</v>
       </c>
     </row>
     <row r="47">
@@ -2172,15 +2736,27 @@
         <v>4</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>сентябрь 2028</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>24.5</v>
+        <v>2</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>июнь 2028</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>21.5</v>
       </c>
     </row>
     <row r="48">
@@ -2208,15 +2784,27 @@
         <v>240</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>2833</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>ноябрь 2028</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>26.1</v>
+        <v>120</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="L48" s="6" t="n">
+        <v>2173</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>август 2028</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>23.1</v>
       </c>
     </row>
     <row r="49">
@@ -2244,15 +2832,27 @@
         <v>62</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>830</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>декабрь 2028</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>27.9</v>
+        <v>31</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="L49" s="6" t="n">
+        <v>660</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>ноябрь 2028</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>26.2</v>
       </c>
     </row>
     <row r="50">
@@ -2280,15 +2880,27 @@
         <v>96</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>1350</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>февраль 2029</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>29.1</v>
+        <v>48</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="L50" s="6" t="n">
+        <v>1086</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>декабрь 2028</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>27.1</v>
       </c>
     </row>
     <row r="51">
@@ -2316,15 +2928,27 @@
         <v>46</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>674</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>март 2029</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>30.3</v>
+        <v>23</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="L51" s="6" t="n">
+        <v>548</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>декабрь 2028</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>27.6</v>
       </c>
     </row>
     <row r="52">
@@ -2352,15 +2976,27 @@
         <v>398</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>6185</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>май 2029</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>32.1</v>
+        <v>199</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>398</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>298</v>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="L52" s="6" t="n">
+        <v>5091</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>февраль 2029</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="53">
@@ -2388,14 +3024,26 @@
         <v>4</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="I53" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K53" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L53" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>больше 3 лет</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="N53" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2424,14 +3072,26 @@
         <v>6</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>304</v>
-      </c>
-      <c r="I54" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>288</v>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t>больше 3 лет</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="N54" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2460,14 +3120,26 @@
         <v>56</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>9339</v>
-      </c>
-      <c r="I55" t="inlineStr">
+        <v>28</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>9185</v>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t>больше 3 лет</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="N55" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2496,14 +3168,26 @@
         <v>4</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>998</v>
-      </c>
-      <c r="I56" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>987</v>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t>больше 3 лет</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="N56" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2532,14 +3216,26 @@
         <v>14</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>928</v>
-      </c>
-      <c r="I57" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>890</v>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t>больше 3 лет</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="N57" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2568,14 +3264,26 @@
         <v>2</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>294</v>
-      </c>
-      <c r="I58" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="6" t="n">
+        <v>288</v>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t>больше 3 лет</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="N58" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2604,14 +3312,26 @@
         <v>34</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>1281</v>
-      </c>
-      <c r="I59" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="L59" s="6" t="n">
+        <v>1187</v>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t>больше 3 лет</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="N59" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2640,14 +3360,26 @@
         <v>10</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>372</v>
-      </c>
-      <c r="I60" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L60" s="6" t="n">
+        <v>344</v>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t>больше 3 лет</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="N60" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2676,14 +3408,26 @@
         <v>12</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>581</v>
-      </c>
-      <c r="I61" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K61" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L61" s="6" t="n">
+        <v>548</v>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t>больше 3 лет</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="N61" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2703,15 +3447,19 @@
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="8" t="inlineStr"/>
       <c r="G62" s="8" t="inlineStr"/>
-      <c r="H62" s="8" t="n">
+      <c r="H62" s="8" t="inlineStr"/>
+      <c r="I62" s="8" t="inlineStr"/>
+      <c r="J62" s="8" t="inlineStr"/>
+      <c r="K62" s="8" t="inlineStr"/>
+      <c r="L62" s="8" t="n">
         <v>117</v>
       </c>
-      <c r="I62" s="7" t="inlineStr">
+      <c r="M62" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J62" s="7" t="inlineStr"/>
+      <c r="N62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -2729,15 +3477,19 @@
       <c r="E63" s="8" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr"/>
       <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="7" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr"/>
+      <c r="I63" s="8" t="inlineStr"/>
+      <c r="J63" s="8" t="inlineStr"/>
+      <c r="K63" s="8" t="inlineStr"/>
+      <c r="L63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J63" s="7" t="inlineStr"/>
+      <c r="N63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -2755,15 +3507,19 @@
       <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="8" t="inlineStr"/>
       <c r="G64" s="8" t="inlineStr"/>
-      <c r="H64" s="8" t="n">
+      <c r="H64" s="8" t="inlineStr"/>
+      <c r="I64" s="8" t="inlineStr"/>
+      <c r="J64" s="8" t="inlineStr"/>
+      <c r="K64" s="8" t="inlineStr"/>
+      <c r="L64" s="8" t="n">
         <v>428</v>
       </c>
-      <c r="I64" s="7" t="inlineStr">
+      <c r="M64" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J64" s="7" t="inlineStr"/>
+      <c r="N64" s="7" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -2781,15 +3537,19 @@
       <c r="E65" s="8" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr"/>
       <c r="G65" s="8" t="inlineStr"/>
-      <c r="H65" s="8" t="n">
+      <c r="H65" s="8" t="inlineStr"/>
+      <c r="I65" s="8" t="inlineStr"/>
+      <c r="J65" s="8" t="inlineStr"/>
+      <c r="K65" s="8" t="inlineStr"/>
+      <c r="L65" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="I65" s="7" t="inlineStr">
+      <c r="M65" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J65" s="7" t="inlineStr"/>
+      <c r="N65" s="7" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -2807,15 +3567,19 @@
       <c r="E66" s="8" t="inlineStr"/>
       <c r="F66" s="8" t="inlineStr"/>
       <c r="G66" s="8" t="inlineStr"/>
-      <c r="H66" s="8" t="n">
+      <c r="H66" s="8" t="inlineStr"/>
+      <c r="I66" s="8" t="inlineStr"/>
+      <c r="J66" s="8" t="inlineStr"/>
+      <c r="K66" s="8" t="inlineStr"/>
+      <c r="L66" s="8" t="n">
         <v>360</v>
       </c>
-      <c r="I66" s="7" t="inlineStr">
+      <c r="M66" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J66" s="7" t="inlineStr"/>
+      <c r="N66" s="7" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -2833,15 +3597,19 @@
       <c r="E67" s="8" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr"/>
       <c r="G67" s="8" t="inlineStr"/>
-      <c r="H67" s="8" t="n">
+      <c r="H67" s="8" t="inlineStr"/>
+      <c r="I67" s="8" t="inlineStr"/>
+      <c r="J67" s="8" t="inlineStr"/>
+      <c r="K67" s="8" t="inlineStr"/>
+      <c r="L67" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="I67" s="7" t="inlineStr">
+      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J67" s="7" t="inlineStr"/>
+      <c r="N67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -2859,15 +3627,19 @@
       <c r="E68" s="8" t="inlineStr"/>
       <c r="F68" s="8" t="inlineStr"/>
       <c r="G68" s="8" t="inlineStr"/>
-      <c r="H68" s="8" t="n">
+      <c r="H68" s="8" t="inlineStr"/>
+      <c r="I68" s="8" t="inlineStr"/>
+      <c r="J68" s="8" t="inlineStr"/>
+      <c r="K68" s="8" t="inlineStr"/>
+      <c r="L68" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="I68" s="7" t="inlineStr">
+      <c r="M68" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J68" s="7" t="inlineStr"/>
+      <c r="N68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -2885,15 +3657,19 @@
       <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr"/>
       <c r="G69" s="8" t="inlineStr"/>
-      <c r="H69" s="8" t="n">
+      <c r="H69" s="8" t="inlineStr"/>
+      <c r="I69" s="8" t="inlineStr"/>
+      <c r="J69" s="8" t="inlineStr"/>
+      <c r="K69" s="8" t="inlineStr"/>
+      <c r="L69" s="8" t="n">
         <v>156</v>
       </c>
-      <c r="I69" s="7" t="inlineStr">
+      <c r="M69" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J69" s="7" t="inlineStr"/>
+      <c r="N69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -2911,15 +3687,19 @@
       <c r="E70" s="8" t="inlineStr"/>
       <c r="F70" s="8" t="inlineStr"/>
       <c r="G70" s="8" t="inlineStr"/>
-      <c r="H70" s="8" t="n">
+      <c r="H70" s="8" t="inlineStr"/>
+      <c r="I70" s="8" t="inlineStr"/>
+      <c r="J70" s="8" t="inlineStr"/>
+      <c r="K70" s="8" t="inlineStr"/>
+      <c r="L70" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I70" s="7" t="inlineStr">
+      <c r="M70" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J70" s="7" t="inlineStr"/>
+      <c r="N70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -2937,15 +3717,19 @@
       <c r="E71" s="8" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr"/>
       <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="8" t="n">
+      <c r="H71" s="8" t="inlineStr"/>
+      <c r="I71" s="8" t="inlineStr"/>
+      <c r="J71" s="8" t="inlineStr"/>
+      <c r="K71" s="8" t="inlineStr"/>
+      <c r="L71" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I71" s="7" t="inlineStr">
+      <c r="M71" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J71" s="7" t="inlineStr"/>
+      <c r="N71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
@@ -2963,15 +3747,19 @@
       <c r="E72" s="8" t="inlineStr"/>
       <c r="F72" s="8" t="inlineStr"/>
       <c r="G72" s="8" t="inlineStr"/>
-      <c r="H72" s="8" t="n">
+      <c r="H72" s="8" t="inlineStr"/>
+      <c r="I72" s="8" t="inlineStr"/>
+      <c r="J72" s="8" t="inlineStr"/>
+      <c r="K72" s="8" t="inlineStr"/>
+      <c r="L72" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I72" s="7" t="inlineStr">
+      <c r="M72" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J72" s="7" t="inlineStr"/>
+      <c r="N72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
@@ -2989,15 +3777,19 @@
       <c r="E73" s="8" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr"/>
       <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="8" t="n">
+      <c r="H73" s="8" t="inlineStr"/>
+      <c r="I73" s="8" t="inlineStr"/>
+      <c r="J73" s="8" t="inlineStr"/>
+      <c r="K73" s="8" t="inlineStr"/>
+      <c r="L73" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I73" s="7" t="inlineStr">
+      <c r="M73" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J73" s="7" t="inlineStr"/>
+      <c r="N73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -3015,15 +3807,19 @@
       <c r="E74" s="8" t="inlineStr"/>
       <c r="F74" s="8" t="inlineStr"/>
       <c r="G74" s="8" t="inlineStr"/>
-      <c r="H74" s="8" t="n">
+      <c r="H74" s="8" t="inlineStr"/>
+      <c r="I74" s="8" t="inlineStr"/>
+      <c r="J74" s="8" t="inlineStr"/>
+      <c r="K74" s="8" t="inlineStr"/>
+      <c r="L74" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I74" s="7" t="inlineStr">
+      <c r="M74" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J74" s="7" t="inlineStr"/>
+      <c r="N74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
@@ -3041,15 +3837,19 @@
       <c r="E75" s="8" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr"/>
       <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="8" t="n">
+      <c r="H75" s="8" t="inlineStr"/>
+      <c r="I75" s="8" t="inlineStr"/>
+      <c r="J75" s="8" t="inlineStr"/>
+      <c r="K75" s="8" t="inlineStr"/>
+      <c r="L75" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I75" s="7" t="inlineStr">
+      <c r="M75" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J75" s="7" t="inlineStr"/>
+      <c r="N75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -3067,15 +3867,19 @@
       <c r="E76" s="8" t="inlineStr"/>
       <c r="F76" s="8" t="inlineStr"/>
       <c r="G76" s="8" t="inlineStr"/>
-      <c r="H76" s="8" t="n">
+      <c r="H76" s="8" t="inlineStr"/>
+      <c r="I76" s="8" t="inlineStr"/>
+      <c r="J76" s="8" t="inlineStr"/>
+      <c r="K76" s="8" t="inlineStr"/>
+      <c r="L76" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I76" s="7" t="inlineStr">
+      <c r="M76" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J76" s="7" t="inlineStr"/>
+      <c r="N76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -3093,15 +3897,19 @@
       <c r="E77" s="8" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr"/>
       <c r="G77" s="8" t="inlineStr"/>
-      <c r="H77" s="8" t="n">
+      <c r="H77" s="8" t="inlineStr"/>
+      <c r="I77" s="8" t="inlineStr"/>
+      <c r="J77" s="8" t="inlineStr"/>
+      <c r="K77" s="8" t="inlineStr"/>
+      <c r="L77" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I77" s="7" t="inlineStr">
+      <c r="M77" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J77" s="7" t="inlineStr"/>
+      <c r="N77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -3119,15 +3927,19 @@
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="8" t="inlineStr"/>
       <c r="G78" s="8" t="inlineStr"/>
-      <c r="H78" s="8" t="n">
+      <c r="H78" s="8" t="inlineStr"/>
+      <c r="I78" s="8" t="inlineStr"/>
+      <c r="J78" s="8" t="inlineStr"/>
+      <c r="K78" s="8" t="inlineStr"/>
+      <c r="L78" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I78" s="7" t="inlineStr">
+      <c r="M78" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J78" s="7" t="inlineStr"/>
+      <c r="N78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -3145,15 +3957,19 @@
       <c r="E79" s="8" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr"/>
       <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="8" t="n">
+      <c r="H79" s="8" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr"/>
+      <c r="J79" s="8" t="inlineStr"/>
+      <c r="K79" s="8" t="inlineStr"/>
+      <c r="L79" s="8" t="n">
         <v>260</v>
       </c>
-      <c r="I79" s="7" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J79" s="7" t="inlineStr"/>
+      <c r="N79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -3171,15 +3987,19 @@
       <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" s="8" t="inlineStr"/>
       <c r="G80" s="8" t="inlineStr"/>
-      <c r="H80" s="8" t="n">
+      <c r="H80" s="8" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr"/>
+      <c r="J80" s="8" t="inlineStr"/>
+      <c r="K80" s="8" t="inlineStr"/>
+      <c r="L80" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="I80" s="7" t="inlineStr">
+      <c r="M80" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J80" s="7" t="inlineStr"/>
+      <c r="N80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -3197,15 +4017,19 @@
       <c r="E81" s="8" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr"/>
       <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="8" t="n">
+      <c r="H81" s="8" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr"/>
+      <c r="J81" s="8" t="inlineStr"/>
+      <c r="K81" s="8" t="inlineStr"/>
+      <c r="L81" s="8" t="n">
         <v>344</v>
       </c>
-      <c r="I81" s="7" t="inlineStr">
+      <c r="M81" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J81" s="7" t="inlineStr"/>
+      <c r="N81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
@@ -3223,15 +4047,19 @@
       <c r="E82" s="8" t="inlineStr"/>
       <c r="F82" s="8" t="inlineStr"/>
       <c r="G82" s="8" t="inlineStr"/>
-      <c r="H82" s="8" t="n">
+      <c r="H82" s="8" t="inlineStr"/>
+      <c r="I82" s="8" t="inlineStr"/>
+      <c r="J82" s="8" t="inlineStr"/>
+      <c r="K82" s="8" t="inlineStr"/>
+      <c r="L82" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="I82" s="7" t="inlineStr">
+      <c r="M82" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J82" s="7" t="inlineStr"/>
+      <c r="N82" s="7" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
@@ -3249,15 +4077,19 @@
       <c r="E83" s="8" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr"/>
       <c r="G83" s="8" t="inlineStr"/>
-      <c r="H83" s="8" t="n">
+      <c r="H83" s="8" t="inlineStr"/>
+      <c r="I83" s="8" t="inlineStr"/>
+      <c r="J83" s="8" t="inlineStr"/>
+      <c r="K83" s="8" t="inlineStr"/>
+      <c r="L83" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="I83" s="7" t="inlineStr">
+      <c r="M83" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J83" s="7" t="inlineStr"/>
+      <c r="N83" s="7" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -3275,15 +4107,19 @@
       <c r="E84" s="8" t="inlineStr"/>
       <c r="F84" s="8" t="inlineStr"/>
       <c r="G84" s="8" t="inlineStr"/>
-      <c r="H84" s="8" t="n">
+      <c r="H84" s="8" t="inlineStr"/>
+      <c r="I84" s="8" t="inlineStr"/>
+      <c r="J84" s="8" t="inlineStr"/>
+      <c r="K84" s="8" t="inlineStr"/>
+      <c r="L84" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I84" s="7" t="inlineStr">
+      <c r="M84" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J84" s="7" t="inlineStr"/>
+      <c r="N84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -3301,15 +4137,19 @@
       <c r="E85" s="8" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr"/>
       <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="8" t="n">
+      <c r="H85" s="8" t="inlineStr"/>
+      <c r="I85" s="8" t="inlineStr"/>
+      <c r="J85" s="8" t="inlineStr"/>
+      <c r="K85" s="8" t="inlineStr"/>
+      <c r="L85" s="8" t="n">
         <v>89</v>
       </c>
-      <c r="I85" s="7" t="inlineStr">
+      <c r="M85" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J85" s="7" t="inlineStr"/>
+      <c r="N85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
@@ -3327,15 +4167,19 @@
       <c r="E86" s="8" t="inlineStr"/>
       <c r="F86" s="8" t="inlineStr"/>
       <c r="G86" s="8" t="inlineStr"/>
-      <c r="H86" s="8" t="n">
+      <c r="H86" s="8" t="inlineStr"/>
+      <c r="I86" s="8" t="inlineStr"/>
+      <c r="J86" s="8" t="inlineStr"/>
+      <c r="K86" s="8" t="inlineStr"/>
+      <c r="L86" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I86" s="7" t="inlineStr">
+      <c r="M86" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J86" s="7" t="inlineStr"/>
+      <c r="N86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
@@ -3353,15 +4197,19 @@
       <c r="E87" s="8" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr"/>
       <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="8" t="n">
+      <c r="H87" s="8" t="inlineStr"/>
+      <c r="I87" s="8" t="inlineStr"/>
+      <c r="J87" s="8" t="inlineStr"/>
+      <c r="K87" s="8" t="inlineStr"/>
+      <c r="L87" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I87" s="7" t="inlineStr">
+      <c r="M87" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J87" s="7" t="inlineStr"/>
+      <c r="N87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
@@ -3379,15 +4227,19 @@
       <c r="E88" s="8" t="inlineStr"/>
       <c r="F88" s="8" t="inlineStr"/>
       <c r="G88" s="8" t="inlineStr"/>
-      <c r="H88" s="8" t="n">
+      <c r="H88" s="8" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr"/>
+      <c r="J88" s="8" t="inlineStr"/>
+      <c r="K88" s="8" t="inlineStr"/>
+      <c r="L88" s="8" t="n">
         <v>180</v>
       </c>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J88" s="7" t="inlineStr"/>
+      <c r="N88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -3405,15 +4257,19 @@
       <c r="E89" s="8" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr"/>
       <c r="G89" s="8" t="inlineStr"/>
-      <c r="H89" s="8" t="n">
+      <c r="H89" s="8" t="inlineStr"/>
+      <c r="I89" s="8" t="inlineStr"/>
+      <c r="J89" s="8" t="inlineStr"/>
+      <c r="K89" s="8" t="inlineStr"/>
+      <c r="L89" s="8" t="n">
         <v>360</v>
       </c>
-      <c r="I89" s="7" t="inlineStr">
+      <c r="M89" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J89" s="7" t="inlineStr"/>
+      <c r="N89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
@@ -3431,15 +4287,19 @@
       <c r="E90" s="8" t="inlineStr"/>
       <c r="F90" s="8" t="inlineStr"/>
       <c r="G90" s="8" t="inlineStr"/>
-      <c r="H90" s="8" t="n">
+      <c r="H90" s="8" t="inlineStr"/>
+      <c r="I90" s="8" t="inlineStr"/>
+      <c r="J90" s="8" t="inlineStr"/>
+      <c r="K90" s="8" t="inlineStr"/>
+      <c r="L90" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="I90" s="7" t="inlineStr">
+      <c r="M90" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J90" s="7" t="inlineStr"/>
+      <c r="N90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -3457,15 +4317,19 @@
       <c r="E91" s="8" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr"/>
       <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="8" t="n">
+      <c r="H91" s="8" t="inlineStr"/>
+      <c r="I91" s="8" t="inlineStr"/>
+      <c r="J91" s="8" t="inlineStr"/>
+      <c r="K91" s="8" t="inlineStr"/>
+      <c r="L91" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="I91" s="7" t="inlineStr">
+      <c r="M91" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J91" s="7" t="inlineStr"/>
+      <c r="N91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -3483,15 +4347,19 @@
       <c r="E92" s="8" t="inlineStr"/>
       <c r="F92" s="8" t="inlineStr"/>
       <c r="G92" s="8" t="inlineStr"/>
-      <c r="H92" s="8" t="n">
+      <c r="H92" s="8" t="inlineStr"/>
+      <c r="I92" s="8" t="inlineStr"/>
+      <c r="J92" s="8" t="inlineStr"/>
+      <c r="K92" s="8" t="inlineStr"/>
+      <c r="L92" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="I92" s="7" t="inlineStr">
+      <c r="M92" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J92" s="7" t="inlineStr"/>
+      <c r="N92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
@@ -3509,15 +4377,19 @@
       <c r="E93" s="8" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr"/>
       <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="8" t="n">
+      <c r="H93" s="8" t="inlineStr"/>
+      <c r="I93" s="8" t="inlineStr"/>
+      <c r="J93" s="8" t="inlineStr"/>
+      <c r="K93" s="8" t="inlineStr"/>
+      <c r="L93" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="I93" s="7" t="inlineStr">
+      <c r="M93" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J93" s="7" t="inlineStr"/>
+      <c r="N93" s="7" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
@@ -3535,15 +4407,19 @@
       <c r="E94" s="8" t="inlineStr"/>
       <c r="F94" s="8" t="inlineStr"/>
       <c r="G94" s="8" t="inlineStr"/>
-      <c r="H94" s="8" t="n">
+      <c r="H94" s="8" t="inlineStr"/>
+      <c r="I94" s="8" t="inlineStr"/>
+      <c r="J94" s="8" t="inlineStr"/>
+      <c r="K94" s="8" t="inlineStr"/>
+      <c r="L94" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I94" s="7" t="inlineStr">
+      <c r="M94" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J94" s="7" t="inlineStr"/>
+      <c r="N94" s="7" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
@@ -3561,15 +4437,19 @@
       <c r="E95" s="8" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr"/>
       <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="8" t="n">
+      <c r="H95" s="8" t="inlineStr"/>
+      <c r="I95" s="8" t="inlineStr"/>
+      <c r="J95" s="8" t="inlineStr"/>
+      <c r="K95" s="8" t="inlineStr"/>
+      <c r="L95" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="M95" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J95" s="7" t="inlineStr"/>
+      <c r="N95" s="7" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
@@ -3587,15 +4467,19 @@
       <c r="E96" s="8" t="inlineStr"/>
       <c r="F96" s="8" t="inlineStr"/>
       <c r="G96" s="8" t="inlineStr"/>
-      <c r="H96" s="8" t="n">
+      <c r="H96" s="8" t="inlineStr"/>
+      <c r="I96" s="8" t="inlineStr"/>
+      <c r="J96" s="8" t="inlineStr"/>
+      <c r="K96" s="8" t="inlineStr"/>
+      <c r="L96" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="I96" s="7" t="inlineStr">
+      <c r="M96" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J96" s="7" t="inlineStr"/>
+      <c r="N96" s="7" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
@@ -3613,15 +4497,19 @@
       <c r="E97" s="8" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr"/>
       <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="8" t="n">
+      <c r="H97" s="8" t="inlineStr"/>
+      <c r="I97" s="8" t="inlineStr"/>
+      <c r="J97" s="8" t="inlineStr"/>
+      <c r="K97" s="8" t="inlineStr"/>
+      <c r="L97" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="I97" s="7" t="inlineStr">
+      <c r="M97" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J97" s="7" t="inlineStr"/>
+      <c r="N97" s="7" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -3639,15 +4527,19 @@
       <c r="E98" s="8" t="inlineStr"/>
       <c r="F98" s="8" t="inlineStr"/>
       <c r="G98" s="8" t="inlineStr"/>
-      <c r="H98" s="8" t="n">
+      <c r="H98" s="8" t="inlineStr"/>
+      <c r="I98" s="8" t="inlineStr"/>
+      <c r="J98" s="8" t="inlineStr"/>
+      <c r="K98" s="8" t="inlineStr"/>
+      <c r="L98" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="I98" s="7" t="inlineStr">
+      <c r="M98" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J98" s="7" t="inlineStr"/>
+      <c r="N98" s="7" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -3665,15 +4557,19 @@
       <c r="E99" s="8" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr"/>
       <c r="G99" s="8" t="inlineStr"/>
-      <c r="H99" s="8" t="n">
+      <c r="H99" s="8" t="inlineStr"/>
+      <c r="I99" s="8" t="inlineStr"/>
+      <c r="J99" s="8" t="inlineStr"/>
+      <c r="K99" s="8" t="inlineStr"/>
+      <c r="L99" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I99" s="7" t="inlineStr">
+      <c r="M99" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J99" s="7" t="inlineStr"/>
+      <c r="N99" s="7" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
@@ -3691,15 +4587,19 @@
       <c r="E100" s="8" t="inlineStr"/>
       <c r="F100" s="8" t="inlineStr"/>
       <c r="G100" s="8" t="inlineStr"/>
-      <c r="H100" s="8" t="n">
+      <c r="H100" s="8" t="inlineStr"/>
+      <c r="I100" s="8" t="inlineStr"/>
+      <c r="J100" s="8" t="inlineStr"/>
+      <c r="K100" s="8" t="inlineStr"/>
+      <c r="L100" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I100" s="7" t="inlineStr">
+      <c r="M100" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J100" s="7" t="inlineStr"/>
+      <c r="N100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
@@ -3717,15 +4617,19 @@
       <c r="E101" s="8" t="inlineStr"/>
       <c r="F101" s="8" t="inlineStr"/>
       <c r="G101" s="8" t="inlineStr"/>
-      <c r="H101" s="8" t="n">
+      <c r="H101" s="8" t="inlineStr"/>
+      <c r="I101" s="8" t="inlineStr"/>
+      <c r="J101" s="8" t="inlineStr"/>
+      <c r="K101" s="8" t="inlineStr"/>
+      <c r="L101" s="8" t="n">
         <v>1190</v>
       </c>
-      <c r="I101" s="7" t="inlineStr">
+      <c r="M101" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J101" s="7" t="inlineStr"/>
+      <c r="N101" s="7" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
@@ -3743,15 +4647,19 @@
       <c r="E102" s="8" t="inlineStr"/>
       <c r="F102" s="8" t="inlineStr"/>
       <c r="G102" s="8" t="inlineStr"/>
-      <c r="H102" s="8" t="n">
+      <c r="H102" s="8" t="inlineStr"/>
+      <c r="I102" s="8" t="inlineStr"/>
+      <c r="J102" s="8" t="inlineStr"/>
+      <c r="K102" s="8" t="inlineStr"/>
+      <c r="L102" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="I102" s="7" t="inlineStr">
+      <c r="M102" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J102" s="7" t="inlineStr"/>
+      <c r="N102" s="7" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
@@ -3769,15 +4677,19 @@
       <c r="E103" s="8" t="inlineStr"/>
       <c r="F103" s="8" t="inlineStr"/>
       <c r="G103" s="8" t="inlineStr"/>
-      <c r="H103" s="8" t="n">
+      <c r="H103" s="8" t="inlineStr"/>
+      <c r="I103" s="8" t="inlineStr"/>
+      <c r="J103" s="8" t="inlineStr"/>
+      <c r="K103" s="8" t="inlineStr"/>
+      <c r="L103" s="8" t="n">
         <v>397</v>
       </c>
-      <c r="I103" s="7" t="inlineStr">
+      <c r="M103" s="7" t="inlineStr">
         <is>
           <t>нет продаж в августе</t>
         </is>
       </c>
-      <c r="J103" s="7" t="inlineStr"/>
+      <c r="N103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
@@ -3804,10 +4716,22 @@
         <v>10588</v>
       </c>
       <c r="H104" s="10" t="n">
-        <v>73573</v>
-      </c>
-      <c r="I104" s="9" t="inlineStr"/>
-      <c r="J104" s="9" t="inlineStr"/>
+        <v>3792</v>
+      </c>
+      <c r="I104" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>5024</v>
+      </c>
+      <c r="K104" s="10" t="n">
+        <v>2304</v>
+      </c>
+      <c r="L104" s="10" t="n">
+        <v>55095</v>
+      </c>
+      <c r="M104" s="9" t="inlineStr"/>
+      <c r="N104" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3820,7 +4744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="92" customWidth="1" min="1" max="1"/>
@@ -3828,11 +4752,15 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3873,15 +4801,35 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток на 01.01, шт</t>
+          <t>Январь</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Февраль х2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Март х1,5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток на 01.05, шт</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Хватит до</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Запас, месяцев</t>
         </is>
@@ -3914,12 +4862,24 @@
       <c r="H2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>сентябрь 2026</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3950,12 +4910,24 @@
       <c r="H3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>сентябрь 2026</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3986,12 +4958,24 @@
       <c r="H4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>октябрь 2026</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="N4" s="2" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -4022,12 +5006,24 @@
       <c r="H5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>октябрь 2026</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="N5" s="2" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -4058,12 +5054,24 @@
       <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>октябрь 2026</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="N6" s="2" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -4094,12 +5102,24 @@
       <c r="H7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="N7" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4130,12 +5150,24 @@
       <c r="H8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -4166,12 +5198,24 @@
       <c r="H9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -4202,12 +5246,24 @@
       <c r="H10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="N10" s="2" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -4238,12 +5294,24 @@
       <c r="H11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="N11" s="2" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -4274,12 +5342,24 @@
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="N12" s="2" t="n">
         <v>2.7</v>
       </c>
     </row>
@@ -4310,12 +5390,24 @@
       <c r="H13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>ноябрь 2026</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="N13" s="2" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -4346,12 +5438,24 @@
       <c r="H14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>декабрь 2026</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="N14" s="2" t="n">
         <v>3.5</v>
       </c>
     </row>
@@ -4382,12 +5486,24 @@
       <c r="H15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>декабрь 2026</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="N15" s="2" t="n">
         <v>3.5</v>
       </c>
     </row>
@@ -4418,12 +5534,24 @@
       <c r="H16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>декабрь 2026</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="N16" s="2" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -4454,12 +5582,24 @@
       <c r="H17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>декабрь 2026</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="N17" s="2" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -4490,12 +5630,24 @@
       <c r="H18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>декабрь 2026</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="N18" s="2" t="n">
         <v>3.9</v>
       </c>
     </row>
@@ -4526,13 +5678,649 @@
       <c r="H19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>декабрь 2026</t>
         </is>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="N19" s="2" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>январь 2027</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>январь 2027</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>624</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>февраль 2027</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>февраль 2027</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>февраль 2027</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>март 2027</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3112</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>342</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>342</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>342</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>513</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>684</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>342</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>684</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>март 2027</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>901</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>март 2027</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>259</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>март 2027</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3239</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>488</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>476</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>март 2027</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>7340</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>709</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>709</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>709</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1064</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1418</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>709</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1418</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>1064</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>апрель 2027</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>759</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>апрель 2027</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>6179</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>844</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>1126</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>1126</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>844</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>549</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>апрель 2027</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
